--- a/artfynd/A 1541-2025 artfynd.xlsx
+++ b/artfynd/A 1541-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128516155</v>
       </c>
       <c r="B2" t="n">
-        <v>79242</v>
+        <v>79246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128516161</v>
       </c>
       <c r="B3" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128515906</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128516360</v>
       </c>
       <c r="B5" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128516112</v>
       </c>
       <c r="B6" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>128516276</v>
       </c>
       <c r="B7" t="n">
-        <v>75163</v>
+        <v>75167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>128516459</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>128516106</v>
       </c>
       <c r="B9" t="n">
-        <v>75176</v>
+        <v>75180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1541-2025 artfynd.xlsx
+++ b/artfynd/A 1541-2025 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>128516360</v>
       </c>
       <c r="B5" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1541-2025 artfynd.xlsx
+++ b/artfynd/A 1541-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128516155</v>
       </c>
       <c r="B2" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128516161</v>
       </c>
       <c r="B3" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128515906</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128516360</v>
       </c>
       <c r="B5" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128516112</v>
       </c>
       <c r="B6" t="n">
-        <v>75175</v>
+        <v>75177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>128516276</v>
       </c>
       <c r="B7" t="n">
-        <v>75167</v>
+        <v>75169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>128516459</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>128516106</v>
       </c>
       <c r="B9" t="n">
-        <v>75180</v>
+        <v>75182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1541-2025 artfynd.xlsx
+++ b/artfynd/A 1541-2025 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>128516360</v>
       </c>
       <c r="B5" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1541-2025 artfynd.xlsx
+++ b/artfynd/A 1541-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128516155</v>
       </c>
       <c r="B2" t="n">
-        <v>79248</v>
+        <v>79275</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128516161</v>
       </c>
       <c r="B3" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128515906</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128516360</v>
       </c>
       <c r="B5" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128516112</v>
       </c>
       <c r="B6" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>128516276</v>
       </c>
       <c r="B7" t="n">
-        <v>75169</v>
+        <v>75196</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>128516459</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>128516106</v>
       </c>
       <c r="B9" t="n">
-        <v>75182</v>
+        <v>75209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1541-2025 artfynd.xlsx
+++ b/artfynd/A 1541-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128516155</v>
       </c>
       <c r="B2" t="n">
-        <v>79275</v>
+        <v>79279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128516161</v>
       </c>
       <c r="B3" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128515906</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128516360</v>
       </c>
       <c r="B5" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128516112</v>
       </c>
       <c r="B6" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>128516276</v>
       </c>
       <c r="B7" t="n">
-        <v>75196</v>
+        <v>75197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>128516459</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>128516106</v>
       </c>
       <c r="B9" t="n">
-        <v>75209</v>
+        <v>75210</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1541-2025 artfynd.xlsx
+++ b/artfynd/A 1541-2025 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>128516360</v>
       </c>
       <c r="B5" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1541-2025 artfynd.xlsx
+++ b/artfynd/A 1541-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128516155</v>
       </c>
       <c r="B2" t="n">
-        <v>79279</v>
+        <v>79283</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128516161</v>
       </c>
       <c r="B3" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128515906</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128516360</v>
       </c>
       <c r="B5" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128516112</v>
       </c>
       <c r="B6" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>128516276</v>
       </c>
       <c r="B7" t="n">
-        <v>75197</v>
+        <v>75201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>128516459</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>128516106</v>
       </c>
       <c r="B9" t="n">
-        <v>75210</v>
+        <v>75214</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1541-2025 artfynd.xlsx
+++ b/artfynd/A 1541-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128516155</v>
       </c>
       <c r="B2" t="n">
-        <v>79283</v>
+        <v>79188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128516161</v>
       </c>
       <c r="B3" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128515906</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128516360</v>
       </c>
       <c r="B5" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128516112</v>
       </c>
       <c r="B6" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>128516276</v>
       </c>
       <c r="B7" t="n">
-        <v>75201</v>
+        <v>82997</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>128516459</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>128516106</v>
       </c>
       <c r="B9" t="n">
-        <v>75214</v>
+        <v>83010</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1541-2025 artfynd.xlsx
+++ b/artfynd/A 1541-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128516155</v>
       </c>
       <c r="B2" t="n">
-        <v>79188</v>
+        <v>79193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128516161</v>
       </c>
       <c r="B3" t="n">
-        <v>82892</v>
+        <v>82897</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128515906</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128516360</v>
       </c>
       <c r="B5" t="n">
-        <v>91533</v>
+        <v>91538</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128516112</v>
       </c>
       <c r="B6" t="n">
-        <v>83005</v>
+        <v>83010</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>128516276</v>
       </c>
       <c r="B7" t="n">
-        <v>82997</v>
+        <v>83002</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>128516459</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>128516106</v>
       </c>
       <c r="B9" t="n">
-        <v>83010</v>
+        <v>83015</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1541-2025 artfynd.xlsx
+++ b/artfynd/A 1541-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128516155</v>
+        <v>128516276</v>
       </c>
       <c r="B2" t="n">
-        <v>79193</v>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1249</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>391461</v>
+        <v>391529</v>
       </c>
       <c r="R2" t="n">
-        <v>7028004</v>
+        <v>7028082</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128516161</v>
+        <v>128516520</v>
       </c>
       <c r="B3" t="n">
-        <v>82897</v>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>391461</v>
+        <v>391410</v>
       </c>
       <c r="R3" t="n">
-        <v>7028004</v>
+        <v>7028063</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128515906</v>
+        <v>128516155</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>391330</v>
+        <v>391461</v>
       </c>
       <c r="R4" t="n">
-        <v>7027891</v>
+        <v>7028004</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128516360</v>
+        <v>128516161</v>
       </c>
       <c r="B5" t="n">
-        <v>91538</v>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>391593</v>
+        <v>391461</v>
       </c>
       <c r="R5" t="n">
-        <v>7028072</v>
+        <v>7028004</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128516112</v>
+        <v>128516106</v>
       </c>
       <c r="B6" t="n">
-        <v>83010</v>
+        <v>83312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,32 +1189,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128516276</v>
+        <v>128515906</v>
       </c>
       <c r="B7" t="n">
-        <v>83002</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>391529</v>
+        <v>391330</v>
       </c>
       <c r="R7" t="n">
-        <v>7028082</v>
+        <v>7027891</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,11 +1294,11 @@
         <v>128516459</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1393,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128516106</v>
+        <v>128516112</v>
       </c>
       <c r="B9" t="n">
-        <v>83015</v>
+        <v>83307</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1404,21 +1404,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1497,6 +1497,516 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123424784</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ivartjärnen, i blandskog 700 m NNV om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>391800</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7028200</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>1993-07-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1993-07-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikstaxruta 19D6a11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123424785</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ivartjärnen, i blandskog 700 m NNV om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>391800</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7028200</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>1993-07-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>1993-07-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikstaxruta 19D6a11</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123424787</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ivartjärnen, i blandskog 700 m NNV om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>391800</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7028200</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>1993-07-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>1993-07-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikstaxruta 19D6a11</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123424750</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ivartjärnen, i blandskog 700 m NNV om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>391800</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7028200</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>1993-07-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>1993-07-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikstaxruta 19D6a11</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123424760</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ivartjärnen, i blandskog 700 m NNV om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>391800</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7028200</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>1993-07-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>1993-07-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikstaxruta 19D6a11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1541-2025 artfynd.xlsx
+++ b/artfynd/A 1541-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128516276</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128516520</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128516155</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128516161</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128516106</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128515906</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128516112</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128516459</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1598,6 +1643,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123424784</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1700,6 +1750,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123424785</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1802,6 +1857,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123424787</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1904,6 +1964,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123424750</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2006,8 +2071,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123424760</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>